--- a/Excel/CardSpecialConfig.xlsx
+++ b/Excel/CardSpecialConfig.xlsx
@@ -62,7 +62,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>仙鉴·青龙</t>
+    <t>仙鉴青龙</t>
   </si>
   <si>
     <t>2001,2002,2003,2004</t>
@@ -74,25 +74,25 @@
     <t>1,2,3,1</t>
   </si>
   <si>
-    <t>仙鉴·白虎</t>
+    <t>仙鉴白虎</t>
   </si>
   <si>
     <t>2001,2002,2003,2005</t>
   </si>
   <si>
-    <t>仙鉴·朱雀</t>
+    <t>仙鉴朱雀</t>
   </si>
   <si>
     <t>2001,2002,2003,2006</t>
   </si>
   <si>
-    <t>仙鉴·玄武</t>
+    <t>仙鉴玄武</t>
   </si>
   <si>
     <t>2001,2002,2003,2007</t>
   </si>
   <si>
-    <t>仙鉴·麒麟</t>
+    <t>仙鉴麒麟</t>
   </si>
   <si>
     <t>2001,2002,2003,2008</t>
@@ -1318,7 +1318,6 @@
     <row r="12" customHeight="1" spans="4:13">
       <c r="D12" s="2"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="1"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1378,7 +1377,6 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="1"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1420,7 +1418,6 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="1"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>

--- a/Excel/CardSpecialConfig.xlsx
+++ b/Excel/CardSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
@@ -68,9 +68,6 @@
     <t>2001,2002,2003,2004</t>
   </si>
   <si>
-    <t>10,15,20,10</t>
-  </si>
-  <si>
     <t>1,2,3,1</t>
   </si>
   <si>
@@ -89,13 +86,13 @@
     <t>仙鉴玄武</t>
   </si>
   <si>
-    <t>2001,2002,2003,2007</t>
+    <t>2001,2002,2003,2012</t>
   </si>
   <si>
     <t>仙鉴麒麟</t>
   </si>
   <si>
-    <t>2001,2002,2003,2008</t>
+    <t>2001,2002,2003,2010</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1199,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" s="5"/>
     </row>
@@ -1217,16 +1214,16 @@
         <v>1998002</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M7" s="5"/>
     </row>
@@ -1241,16 +1238,16 @@
         <v>1998003</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="5"/>
@@ -1266,16 +1263,16 @@
         <v>1998004</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="5"/>
@@ -1291,16 +1288,16 @@
         <v>1998005</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="5"/>
